--- a/reports/Debug-snowbowl-20251230/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20251230/Week Total (Prior Year)_Visits.xlsx
@@ -557,10 +557,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="C11" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -571,13 +571,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>45656</v>
+        <v>45658</v>
       </c>
       <c r="C12" s="2">
-        <v>272</v>
+        <v>6</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -585,10 +585,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="C13" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -599,13 +599,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="C14" s="2">
-        <v>58</v>
+        <v>322</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -613,10 +613,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>45657</v>
+        <v>45660</v>
       </c>
       <c r="C15" s="2">
-        <v>471</v>
+        <v>13</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -627,10 +627,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C16" s="2">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>5</v>
@@ -641,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="C17" s="2">
         <v>7</v>
@@ -655,13 +655,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>45660</v>
+        <v>45657</v>
       </c>
       <c r="C18" s="2">
-        <v>1426</v>
+        <v>266</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -669,10 +669,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>45662</v>
+        <v>45658</v>
       </c>
       <c r="C19" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -683,13 +683,13 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>45656</v>
+        <v>45658</v>
       </c>
       <c r="C20" s="2">
-        <v>546</v>
+        <v>1102</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -697,13 +697,13 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C21" s="2">
+        <v>236</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -711,13 +711,13 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C22" s="2">
-        <v>1304</v>
+        <v>902</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -725,13 +725,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="C23" s="2">
-        <v>7</v>
+        <v>1268</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -739,13 +739,13 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>45659</v>
+        <v>45656</v>
       </c>
       <c r="C24" s="2">
-        <v>7</v>
+        <v>546</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -753,13 +753,13 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C25" s="2">
-        <v>509</v>
+        <v>7</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>45661</v>
+        <v>45658</v>
       </c>
       <c r="C26" s="2">
-        <v>5</v>
+        <v>1304</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -781,10 +781,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>45662</v>
+        <v>45659</v>
       </c>
       <c r="C27" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>5</v>
@@ -795,10 +795,10 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>45662</v>
+        <v>45659</v>
       </c>
       <c r="C28" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>5</v>
@@ -809,10 +809,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>45662</v>
+        <v>45659</v>
       </c>
       <c r="C29" s="2">
-        <v>239</v>
+        <v>509</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>6</v>
@@ -823,10 +823,10 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>45657</v>
+        <v>45661</v>
       </c>
       <c r="C30" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -837,10 +837,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>45658</v>
+        <v>45662</v>
       </c>
       <c r="C31" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -851,7 +851,7 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>45658</v>
+        <v>45662</v>
       </c>
       <c r="C32" s="2">
         <v>5</v>
@@ -865,10 +865,10 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>45658</v>
+        <v>45662</v>
       </c>
       <c r="C33" s="2">
-        <v>322</v>
+        <v>239</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>6</v>
@@ -879,10 +879,10 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>45660</v>
+        <v>45656</v>
       </c>
       <c r="C34" s="2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -893,13 +893,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>45660</v>
+        <v>45656</v>
       </c>
       <c r="C35" s="2">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -907,10 +907,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>45661</v>
+        <v>45657</v>
       </c>
       <c r="C36" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -924,10 +924,10 @@
         <v>45657</v>
       </c>
       <c r="C37" s="2">
-        <v>266</v>
+        <v>58</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -935,10 +935,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>45658</v>
+        <v>45657</v>
       </c>
       <c r="C38" s="2">
-        <v>10</v>
+        <v>471</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
@@ -952,7 +952,7 @@
         <v>45658</v>
       </c>
       <c r="C39" s="2">
-        <v>1102</v>
+        <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>5</v>
@@ -963,13 +963,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="C40" s="2">
-        <v>236</v>
+        <v>7</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -977,10 +977,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C41" s="2">
-        <v>902</v>
+        <v>1426</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>5</v>
@@ -991,13 +991,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>45661</v>
+        <v>45662</v>
       </c>
       <c r="C42" s="2">
-        <v>1268</v>
+        <v>12</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,10 +1008,10 @@
         <v>45656</v>
       </c>
       <c r="C43" s="2">
-        <v>48</v>
+        <v>1705</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1019,13 +1019,13 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="C44" s="2">
-        <v>1496</v>
+        <v>67</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C45" s="2">
-        <v>247</v>
+        <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,10 +1050,10 @@
         <v>45659</v>
       </c>
       <c r="C46" s="2">
-        <v>52</v>
+        <v>1510</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,10 +1064,10 @@
         <v>45659</v>
       </c>
       <c r="C47" s="2">
-        <v>1069</v>
+        <v>196</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,7 +1078,7 @@
         <v>45660</v>
       </c>
       <c r="C48" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1089,13 +1089,13 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>45660</v>
+        <v>45661</v>
       </c>
       <c r="C49" s="2">
-        <v>1377</v>
+        <v>63</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1103,10 +1103,10 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>45661</v>
+        <v>45662</v>
       </c>
       <c r="C50" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1117,13 +1117,13 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>45661</v>
+        <v>45662</v>
       </c>
       <c r="C51" s="2">
-        <v>248</v>
+        <v>862</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,10 +1134,10 @@
         <v>45662</v>
       </c>
       <c r="C52" s="2">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1145,10 +1145,10 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>45662</v>
+        <v>45656</v>
       </c>
       <c r="C53" s="2">
-        <v>866</v>
+        <v>48</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1159,10 +1159,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="C54" s="2">
-        <v>1705</v>
+        <v>1496</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>8</v>
@@ -1176,10 +1176,10 @@
         <v>45658</v>
       </c>
       <c r="C55" s="2">
-        <v>67</v>
+        <v>247</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,7 +1190,7 @@
         <v>45659</v>
       </c>
       <c r="C56" s="2">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>5</v>
@@ -1204,10 +1204,10 @@
         <v>45659</v>
       </c>
       <c r="C57" s="2">
-        <v>1510</v>
+        <v>1069</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1215,13 +1215,13 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="C58" s="2">
-        <v>196</v>
+        <v>7</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1232,10 +1232,10 @@
         <v>45660</v>
       </c>
       <c r="C59" s="2">
-        <v>6</v>
+        <v>1377</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1246,7 +1246,7 @@
         <v>45661</v>
       </c>
       <c r="C60" s="2">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>5</v>
@@ -1257,13 +1257,13 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>45662</v>
+        <v>45661</v>
       </c>
       <c r="C61" s="2">
-        <v>2</v>
+        <v>248</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,10 +1274,10 @@
         <v>45662</v>
       </c>
       <c r="C62" s="2">
-        <v>862</v>
+        <v>60</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1288,10 +1288,10 @@
         <v>45662</v>
       </c>
       <c r="C63" s="2">
-        <v>57</v>
+        <v>866</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
